--- a/MapTempatDuduk.xlsx
+++ b/MapTempatDuduk.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ivan\Kuliah Brou\Pelajaran\Semester 6\Asdos Praktikum RPL-BO\Randomizer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\Downloads\SomeRandomizer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE3C3A9-63D5-4F7A-93ED-26609FDE2196}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25836D7-745A-4AAC-87FD-FD1CF4EEACB1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Grup B - Lab I" sheetId="1" r:id="rId1"/>
+    <sheet name="Grup A - Lab A" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="7">
   <si>
     <t>PROYEKTOR</t>
   </si>
@@ -53,7 +53,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,12 +96,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
@@ -123,7 +117,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -208,8 +202,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -377,30 +389,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -552,11 +540,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -570,119 +571,54 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -701,22 +637,78 @@
     <xf numFmtId="0" fontId="2" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1017,12 +1009,12 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="46"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="25"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="7"/>
@@ -1036,36 +1028,36 @@
       <c r="R1" s="14"/>
       <c r="S1" s="14"/>
       <c r="T1" s="11"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
     </row>
     <row r="2" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="49"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="28"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="8"/>
       <c r="K2" s="10"/>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="17"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="31"/>
       <c r="T2" s="12"/>
-      <c r="U2" s="55"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="55"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
     </row>
     <row r="3" spans="1:23" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
@@ -1104,146 +1096,164 @@
         <v>3</v>
       </c>
       <c r="T3" s="12"/>
-      <c r="U3" s="55"/>
-      <c r="V3" s="55"/>
-      <c r="W3" s="55"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
     </row>
     <row r="4" spans="1:23" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="B4" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="33"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="41"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
       <c r="J4" s="8"/>
       <c r="K4" s="10"/>
-      <c r="L4" s="20">
+      <c r="L4" s="17">
         <v>1</v>
       </c>
-      <c r="M4" s="21"/>
-      <c r="N4" s="26">
+      <c r="M4" s="41">
+        <v>71251210</v>
+      </c>
+      <c r="N4" s="18">
         <v>13</v>
       </c>
-      <c r="O4" s="27"/>
-      <c r="P4" s="32">
+      <c r="O4" s="50">
+        <v>71251186</v>
+      </c>
+      <c r="P4" s="19">
         <v>25</v>
       </c>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="38">
+      <c r="Q4" s="39">
+        <v>71251208</v>
+      </c>
+      <c r="R4" s="20">
         <v>37</v>
       </c>
-      <c r="S4" s="53" t="s">
-        <v>5</v>
+      <c r="S4" s="21">
+        <v>71251211</v>
       </c>
       <c r="T4" s="12"/>
-      <c r="U4" s="55"/>
-      <c r="V4" s="55"/>
-      <c r="W4" s="55"/>
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="22"/>
     </row>
     <row r="5" spans="1:23" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="43"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="6"/>
       <c r="J5" s="8"/>
       <c r="K5" s="10"/>
-      <c r="L5" s="20">
+      <c r="L5" s="17">
         <v>2</v>
       </c>
-      <c r="M5" s="21"/>
-      <c r="N5" s="26">
+      <c r="M5" s="41">
+        <v>71251181</v>
+      </c>
+      <c r="N5" s="43">
         <v>14</v>
       </c>
-      <c r="O5" s="27"/>
-      <c r="P5" s="32">
+      <c r="O5" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="P5" s="43">
         <v>26</v>
       </c>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="38">
+      <c r="Q5" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="R5" s="43">
         <v>38</v>
       </c>
-      <c r="S5" s="53" t="s">
+      <c r="S5" s="44" t="s">
         <v>5</v>
       </c>
       <c r="T5" s="12"/>
-      <c r="U5" s="55"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="55"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="22"/>
     </row>
     <row r="6" spans="1:23" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="5">
-        <v>6</v>
-      </c>
-      <c r="C6" s="5">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="C6" s="40">
+        <v>2</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="5">
+        <v>3</v>
+      </c>
+      <c r="F6" s="49">
         <v>4</v>
-      </c>
-      <c r="F6" s="5">
-        <v>3</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="5">
-        <v>2</v>
-      </c>
-      <c r="I6" s="5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="I6" s="49">
+        <v>6</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="10"/>
-      <c r="L6" s="20">
+      <c r="L6" s="17">
         <v>3</v>
       </c>
-      <c r="M6" s="21"/>
-      <c r="N6" s="26">
+      <c r="M6" s="41">
+        <v>71251213</v>
+      </c>
+      <c r="N6" s="18">
         <v>15</v>
       </c>
-      <c r="O6" s="27"/>
-      <c r="P6" s="32">
+      <c r="O6" s="50">
+        <v>71251224</v>
+      </c>
+      <c r="P6" s="19">
         <v>27</v>
       </c>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="38">
+      <c r="Q6" s="39">
+        <v>71241157</v>
+      </c>
+      <c r="R6" s="20">
         <v>39</v>
       </c>
-      <c r="S6" s="53" t="s">
-        <v>5</v>
+      <c r="S6" s="21">
+        <v>71251228</v>
       </c>
       <c r="T6" s="12"/>
-      <c r="U6" s="55"/>
-      <c r="V6" s="55"/>
-      <c r="W6" s="55"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="22"/>
     </row>
     <row r="7" spans="1:23" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
-      <c r="B7" s="5">
+      <c r="B7" s="49">
         <v>12</v>
       </c>
       <c r="C7" s="5">
         <v>11</v>
       </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="5">
+      <c r="E7" s="49">
         <v>10</v>
       </c>
       <c r="F7" s="5">
         <v>9</v>
       </c>
       <c r="G7" s="4"/>
-      <c r="H7" s="5">
+      <c r="H7" s="49">
         <v>8</v>
       </c>
       <c r="I7" s="5">
@@ -1251,93 +1261,105 @@
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="10"/>
-      <c r="L7" s="20">
+      <c r="L7" s="43">
         <v>4</v>
       </c>
-      <c r="M7" s="22"/>
-      <c r="N7" s="26">
+      <c r="M7" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="43">
         <v>16</v>
       </c>
-      <c r="O7" s="28"/>
-      <c r="P7" s="32">
+      <c r="O7" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="P7" s="43">
         <v>28</v>
       </c>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="38">
+      <c r="Q7" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="R7" s="43">
         <v>40</v>
       </c>
-      <c r="S7" s="53" t="s">
+      <c r="S7" s="44" t="s">
         <v>5</v>
       </c>
       <c r="T7" s="12"/>
-      <c r="U7" s="55"/>
-      <c r="V7" s="55"/>
-      <c r="W7" s="55"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="22"/>
     </row>
     <row r="8" spans="1:23" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="5">
-        <v>18</v>
-      </c>
-      <c r="C8" s="5">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="C8" s="49">
+        <v>14</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="5">
+        <v>15</v>
+      </c>
+      <c r="F8" s="49">
         <v>16</v>
-      </c>
-      <c r="F8" s="5">
-        <v>15</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="5">
-        <v>14</v>
-      </c>
-      <c r="I8" s="5">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="I8" s="49">
+        <v>18</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="10"/>
-      <c r="L8" s="20">
-        <v>5</v>
-      </c>
-      <c r="M8" s="23"/>
-      <c r="N8" s="26">
+      <c r="L8" s="17">
+        <v>5</v>
+      </c>
+      <c r="M8" s="42">
+        <v>71241086</v>
+      </c>
+      <c r="N8" s="18">
         <v>17</v>
       </c>
-      <c r="O8" s="29"/>
-      <c r="P8" s="32">
+      <c r="O8" s="51">
+        <v>71251177</v>
+      </c>
+      <c r="P8" s="19">
         <v>29</v>
       </c>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="38">
+      <c r="Q8" s="52">
+        <v>71251199</v>
+      </c>
+      <c r="R8" s="20">
         <v>41</v>
       </c>
-      <c r="S8" s="53" t="s">
-        <v>5</v>
+      <c r="S8" s="21">
+        <v>71241113</v>
       </c>
       <c r="T8" s="12"/>
-      <c r="U8" s="55"/>
-      <c r="V8" s="55"/>
-      <c r="W8" s="55"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
     </row>
     <row r="9" spans="1:23" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
-      <c r="B9" s="5">
+      <c r="B9" s="49">
         <v>24</v>
       </c>
       <c r="C9" s="5">
         <v>23</v>
       </c>
       <c r="D9" s="4"/>
-      <c r="E9" s="5">
+      <c r="E9" s="49">
         <v>22</v>
       </c>
       <c r="F9" s="5">
         <v>21</v>
       </c>
       <c r="G9" s="4"/>
-      <c r="H9" s="5">
+      <c r="H9" s="49">
         <v>20</v>
       </c>
       <c r="I9" s="5">
@@ -1345,93 +1367,105 @@
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="10"/>
-      <c r="L9" s="20">
+      <c r="L9" s="43">
         <v>6</v>
       </c>
-      <c r="M9" s="23"/>
-      <c r="N9" s="26">
+      <c r="M9" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="43">
         <v>18</v>
       </c>
-      <c r="O9" s="29"/>
-      <c r="P9" s="32">
+      <c r="O9" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="43">
         <v>30</v>
       </c>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="38">
+      <c r="Q9" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="43">
         <v>42</v>
       </c>
-      <c r="S9" s="53" t="s">
+      <c r="S9" s="44" t="s">
         <v>5</v>
       </c>
       <c r="T9" s="12"/>
-      <c r="U9" s="55"/>
-      <c r="V9" s="55"/>
-      <c r="W9" s="55"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
     </row>
     <row r="10" spans="1:23" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="5">
-        <v>30</v>
-      </c>
-      <c r="C10" s="5">
-        <v>29</v>
+        <v>25</v>
+      </c>
+      <c r="C10" s="49">
+        <v>26</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="5">
+        <v>27</v>
+      </c>
+      <c r="F10" s="49">
         <v>28</v>
-      </c>
-      <c r="F10" s="5">
-        <v>27</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="5">
-        <v>26</v>
-      </c>
-      <c r="I10" s="5">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="I10" s="49">
+        <v>30</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="10"/>
-      <c r="L10" s="20">
+      <c r="L10" s="17">
         <v>7</v>
       </c>
-      <c r="M10" s="23"/>
-      <c r="N10" s="26">
+      <c r="M10" s="42">
+        <v>71251226</v>
+      </c>
+      <c r="N10" s="18">
         <v>19</v>
       </c>
-      <c r="O10" s="29"/>
-      <c r="P10" s="32">
+      <c r="O10" s="51">
+        <v>71251173</v>
+      </c>
+      <c r="P10" s="19">
         <v>31</v>
       </c>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="38">
+      <c r="Q10" s="52">
+        <v>71251232</v>
+      </c>
+      <c r="R10" s="20">
         <v>43</v>
       </c>
-      <c r="S10" s="53" t="s">
-        <v>5</v>
+      <c r="S10" s="21">
+        <v>71251225</v>
       </c>
       <c r="T10" s="12"/>
-      <c r="U10" s="55"/>
-      <c r="V10" s="55"/>
-      <c r="W10" s="55"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
     </row>
     <row r="11" spans="1:23" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
-      <c r="B11" s="5">
+      <c r="B11" s="49">
         <v>36</v>
       </c>
       <c r="C11" s="5">
         <v>35</v>
       </c>
       <c r="D11" s="4"/>
-      <c r="E11" s="5">
+      <c r="E11" s="49">
         <v>34</v>
       </c>
       <c r="F11" s="5">
         <v>33</v>
       </c>
       <c r="G11" s="4"/>
-      <c r="H11" s="5">
+      <c r="H11" s="49">
         <v>32</v>
       </c>
       <c r="I11" s="5">
@@ -1439,122 +1473,140 @@
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="10"/>
-      <c r="L11" s="20">
+      <c r="L11" s="43">
         <v>8</v>
       </c>
-      <c r="M11" s="23"/>
-      <c r="N11" s="26">
+      <c r="M11" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="N11" s="43">
         <v>20</v>
       </c>
-      <c r="O11" s="29"/>
-      <c r="P11" s="32">
+      <c r="O11" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="P11" s="43">
         <v>32</v>
       </c>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="38">
+      <c r="Q11" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="R11" s="43">
         <v>44</v>
       </c>
-      <c r="S11" s="53" t="s">
+      <c r="S11" s="44" t="s">
         <v>5</v>
       </c>
       <c r="T11" s="12"/>
-      <c r="U11" s="55"/>
-      <c r="V11" s="55"/>
-      <c r="W11" s="55"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
     </row>
     <row r="12" spans="1:23" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
-      <c r="B12" s="39">
+      <c r="B12" s="40">
+        <v>37</v>
+      </c>
+      <c r="C12" s="49">
+        <v>38</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="40">
+        <v>39</v>
+      </c>
+      <c r="F12" s="49">
+        <v>40</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="40">
+        <v>41</v>
+      </c>
+      <c r="I12" s="49">
         <v>42</v>
-      </c>
-      <c r="C12" s="39">
-        <v>41</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="39">
-        <v>40</v>
-      </c>
-      <c r="F12" s="39">
-        <v>39</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="39">
-        <v>38</v>
-      </c>
-      <c r="I12" s="39">
-        <v>37</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="10"/>
-      <c r="L12" s="20">
+      <c r="L12" s="17">
         <v>9</v>
       </c>
-      <c r="M12" s="23"/>
-      <c r="N12" s="26">
+      <c r="M12" s="42">
+        <v>71251198</v>
+      </c>
+      <c r="N12" s="18">
         <v>21</v>
       </c>
-      <c r="O12" s="29"/>
-      <c r="P12" s="32">
+      <c r="O12" s="51">
+        <v>71251190</v>
+      </c>
+      <c r="P12" s="19">
         <v>33</v>
       </c>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="38">
+      <c r="Q12" s="52">
+        <v>71251182</v>
+      </c>
+      <c r="R12" s="20">
         <v>45</v>
       </c>
-      <c r="S12" s="53" t="s">
-        <v>5</v>
+      <c r="S12" s="21">
+        <v>71251227</v>
       </c>
       <c r="T12" s="12"/>
-      <c r="U12" s="55"/>
-      <c r="V12" s="55"/>
-      <c r="W12" s="55"/>
+      <c r="U12" s="22"/>
+      <c r="V12" s="22"/>
+      <c r="W12" s="22"/>
     </row>
     <row r="13" spans="1:23" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
-      <c r="B13" s="39">
+      <c r="B13" s="49">
         <v>48</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="40">
         <v>47</v>
       </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="39">
+      <c r="E13" s="49">
         <v>46</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="40">
         <v>45</v>
       </c>
       <c r="G13" s="4"/>
-      <c r="H13" s="39">
+      <c r="H13" s="49">
         <v>44</v>
       </c>
-      <c r="I13" s="39">
+      <c r="I13" s="40">
         <v>43</v>
       </c>
       <c r="J13" s="8"/>
       <c r="K13" s="10"/>
-      <c r="L13" s="20">
+      <c r="L13" s="43">
         <v>10</v>
       </c>
-      <c r="M13" s="24"/>
-      <c r="N13" s="26">
+      <c r="M13" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="N13" s="43">
         <v>22</v>
       </c>
-      <c r="O13" s="30"/>
-      <c r="P13" s="32">
+      <c r="O13" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="P13" s="43">
         <v>34</v>
       </c>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="38">
+      <c r="Q13" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="R13" s="43">
         <v>46</v>
       </c>
-      <c r="S13" s="53" t="s">
+      <c r="S13" s="44" t="s">
         <v>5</v>
       </c>
       <c r="T13" s="12"/>
-      <c r="U13" s="55"/>
-      <c r="V13" s="55"/>
-      <c r="W13" s="55"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
     </row>
     <row r="14" spans="1:23" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
@@ -1568,65 +1620,77 @@
       <c r="I14" s="4"/>
       <c r="J14" s="8"/>
       <c r="K14" s="10"/>
-      <c r="L14" s="20">
+      <c r="L14" s="17">
         <v>11</v>
       </c>
-      <c r="M14" s="21"/>
-      <c r="N14" s="26">
+      <c r="M14" s="41">
+        <v>71241118</v>
+      </c>
+      <c r="N14" s="18">
         <v>23</v>
       </c>
-      <c r="O14" s="27"/>
-      <c r="P14" s="32">
+      <c r="O14" s="50">
+        <v>71251212</v>
+      </c>
+      <c r="P14" s="19">
         <v>35</v>
       </c>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="38">
+      <c r="Q14" s="39">
+        <v>71251192</v>
+      </c>
+      <c r="R14" s="20">
         <v>47</v>
       </c>
-      <c r="S14" s="53" t="s">
-        <v>5</v>
+      <c r="S14" s="21">
+        <v>71251218</v>
       </c>
       <c r="T14" s="12"/>
-      <c r="U14" s="55"/>
-      <c r="V14" s="55"/>
-      <c r="W14" s="55"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
     </row>
-    <row r="15" spans="1:23" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="50" t="s">
+      <c r="B15" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="52"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="8"/>
       <c r="K15" s="10"/>
-      <c r="L15" s="20">
+      <c r="L15" s="43">
         <v>12</v>
       </c>
-      <c r="M15" s="25"/>
-      <c r="N15" s="26">
+      <c r="M15" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="N15" s="43">
         <v>24</v>
       </c>
-      <c r="O15" s="31"/>
-      <c r="P15" s="32">
+      <c r="O15" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="43">
         <v>36</v>
       </c>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="38">
+      <c r="Q15" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="43">
         <v>48</v>
       </c>
-      <c r="S15" s="53" t="s">
+      <c r="S15" s="44" t="s">
         <v>5</v>
       </c>
       <c r="T15" s="12"/>
-      <c r="U15" s="55"/>
-      <c r="V15" s="55"/>
-      <c r="W15" s="55"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
     </row>
     <row r="16" spans="1:23" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
@@ -1640,51 +1704,51 @@
       <c r="I16" s="4"/>
       <c r="J16" s="8"/>
       <c r="K16" s="9"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="54"/>
-      <c r="N16" s="54"/>
-      <c r="O16" s="54"/>
-      <c r="P16" s="54"/>
-      <c r="Q16" s="18"/>
-      <c r="R16" s="18"/>
-      <c r="S16" s="19"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="16"/>
       <c r="T16" s="11"/>
-      <c r="U16" s="55"/>
-      <c r="V16" s="55"/>
-      <c r="W16" s="55"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="55"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="55"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="55"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="55"/>
-      <c r="S17" s="55"/>
-      <c r="T17" s="55"/>
-      <c r="U17" s="55"/>
-      <c r="V17" s="55"/>
-      <c r="W17" s="55"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="D1:G2"/>
     <mergeCell ref="L2:S2"/>
-    <mergeCell ref="H4:I5"/>
-    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="B4:C5"/>
     <mergeCell ref="L16:P16"/>
+    <mergeCell ref="B15:C15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
